--- a/public/nvidia-eccn.xlsx
+++ b/public/nvidia-eccn.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-04-24T07:08:13+00:00</t>
+          <t>2026-04-27T05:39:41+00:00</t>
         </is>
       </c>
     </row>
